--- a/artfynd/A 28515-2023 artfynd.xlsx
+++ b/artfynd/A 28515-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 28515-2023 artfynd.xlsx
+++ b/artfynd/A 28515-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,434 +1141,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112604989</v>
-      </c>
-      <c r="B6" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Dallund, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>670023</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7180374</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112604988</v>
-      </c>
-      <c r="B7" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Dallund, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>670043</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7180402</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112604987</v>
-      </c>
-      <c r="B8" t="n">
-        <v>78919</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Dallund, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>670055</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7180345</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112604986</v>
-      </c>
-      <c r="B9" t="n">
-        <v>89791</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Porodaedalea pini</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Dallund, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>670140</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7180602</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Lycksele</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28515-2023 artfynd.xlsx
+++ b/artfynd/A 28515-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109912948</v>
+        <v>112604986</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>670140.4607435524</v>
+        <v>670140</v>
       </c>
       <c r="R2" t="n">
-        <v>7180602.142509943</v>
+        <v>7180602</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2023-05-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109912950</v>
+        <v>112604987</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>670042.7783862009</v>
+        <v>670054</v>
       </c>
       <c r="R3" t="n">
-        <v>7180401.635120471</v>
+        <v>7180345</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2023-05-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -909,15 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109912949</v>
+        <v>112604988</v>
       </c>
       <c r="B4" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>670054.5610625533</v>
+        <v>670043</v>
       </c>
       <c r="R4" t="n">
-        <v>7180344.86897183</v>
+        <v>7180402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,19 +947,9 @@
           <t>2023-05-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109912951</v>
+        <v>112604989</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>670023.3359087151</v>
+        <v>670023</v>
       </c>
       <c r="R5" t="n">
-        <v>7180373.53833005</v>
+        <v>7180373</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,19 +1049,9 @@
           <t>2023-05-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-05-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 28515-2023 artfynd.xlsx
+++ b/artfynd/A 28515-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112604986</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112604987</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112604988</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112604989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>